--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136088304</v>
       </c>
       <c r="B3" t="n">
-        <v>92098</v>
+        <v>92101</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136088477</v>
       </c>
       <c r="B4" t="n">
-        <v>91622</v>
+        <v>91624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 15461-2023 artfynd.xlsx
+++ b/artfynd/A 15461-2023 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136088304</v>
       </c>
       <c r="B3" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
